--- a/ticket_order_forms/045_ticket_form_ll_2021--ticket_order_forms.xlsx
+++ b/ticket_order_forms/045_ticket_form_ll_2021--ticket_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'ticket_1',_'label':_'ticket_1'}</t>
+          <t>ticket_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Ticket 1', 'label': 'Ticket 1'}</t>
+          <t>Ticket 1</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'ticket_2',_'label':_'ticket_2'}</t>
+          <t>ticket_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Ticket 2', 'label': 'Ticket 2'}</t>
+          <t>Ticket 2</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'ticket_3',_'label':_'ticket_3'}</t>
+          <t>ticket_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Ticket 3', 'label': 'Ticket 3'}</t>
+          <t>Ticket 3</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'status_1',_'label':_'status_1'}</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Status 1', 'label': 'Status 1'}</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'status_2',_'label':_'status_2'}</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Status 2', 'label': 'Status 2'}</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'status_3',_'label':_'status_3'}</t>
+          <t>status_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Status 3', 'label': 'Status 3'}</t>
+          <t>Status 3</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'ticket_1',_'label':_'ticket_1'}</t>
+          <t>ticket_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Ticket 1', 'label': 'Ticket 1'}</t>
+          <t>Ticket 1</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ticket_2',_'label':_'ticket_2'}</t>
+          <t>ticket_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Ticket 2', 'label': 'Ticket 2'}</t>
+          <t>Ticket 2</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'ticket_3',_'label':_'ticket_3'}</t>
+          <t>ticket_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Ticket 3', 'label': 'Ticket 3'}</t>
+          <t>Ticket 3</t>
         </is>
       </c>
     </row>
